--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/Output_appointments_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/Output_appointments_Raw.xlsx
@@ -352,55 +352,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_appts</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_appts</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>median_appts</t>
+          <t>min</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max_appts</t>
+          <t>max</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sd_appts</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1_appts</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>q3_appts</t>
+          <t>lower_q</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
+        <v>20691</v>
+      </c>
+      <c r="B2">
         <v>8.109999999999999</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>1</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
       </c>
       <c r="D2">
         <v>241</v>
@@ -409,10 +429,22 @@
         <v>9.81</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>10</v>
+      </c>
+      <c r="I2">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J2">
+        <v>7.98</v>
+      </c>
+      <c r="K2">
+        <v>8.25</v>
       </c>
     </row>
   </sheetData>
@@ -422,55 +454,75 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_appts</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_appts</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>median_appts</t>
+          <t>min</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max_appts</t>
+          <t>max</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sd_appts</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1_appts</t>
+          <t>median</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>q3_appts</t>
+          <t>lower_q</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
+        <v>23106</v>
+      </c>
+      <c r="B2">
         <v>7.27</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>0</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
       </c>
       <c r="D2">
         <v>241</v>
@@ -479,10 +531,22 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>9</v>
+      </c>
+      <c r="I2">
+        <v>0.06</v>
+      </c>
+      <c r="J2">
+        <v>7.14</v>
+      </c>
+      <c r="K2">
+        <v>7.39</v>
       </c>
     </row>
   </sheetData>
